--- a/backend/uploads/individuales/TRASPLANTE/2/Planilla_2_TRASPLANTE.xlsx
+++ b/backend/uploads/individuales/TRASPLANTE/2/Planilla_2_TRASPLANTE.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
   <si>
     <t>CENTRO CLINICO QUIRÚRGICO AMBULATORIO HOSPITAL DEL DÍA CHIMBACALLE</t>
   </si>
@@ -56,15 +56,27 @@
     <t>CIE 10:</t>
   </si>
   <si>
+    <t>M621</t>
+  </si>
+  <si>
     <t>No. Código de Válidación/ No. Carga</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>No. Identificación</t>
   </si>
   <si>
+    <t>1716560089</t>
+  </si>
+  <si>
     <t>Beneficiario:</t>
   </si>
   <si>
+    <t>DELGADO VALLEJO JORGE WASHINGTON</t>
+  </si>
+  <si>
     <t>Detalle de servicios:</t>
   </si>
   <si>
@@ -101,25 +113,25 @@
     <t>TOTAL SOLICITADO</t>
   </si>
   <si>
-    <t>2025-04-15</t>
+    <t>3214001002</t>
+  </si>
+  <si>
+    <t>EM12-45</t>
+  </si>
+  <si>
+    <t>3432620076180</t>
+  </si>
+  <si>
+    <t>EM09-38</t>
+  </si>
+  <si>
+    <t>3432620068050</t>
   </si>
   <si>
     <t>3432620127040</t>
   </si>
   <si>
-    <t>VENDA ADHESIVA ELASTICA, 6</t>
-  </si>
-  <si>
-    <t>397164</t>
-  </si>
-  <si>
-    <t>Ambulancia pago por Km recorrido ida y vuelta,  más de 20 km.</t>
-  </si>
-  <si>
-    <t>3432620068050</t>
-  </si>
-  <si>
-    <t>Guantes de Latex, Talla Peque??o</t>
+    <t>SA09-38</t>
   </si>
   <si>
     <t>397153</t>
@@ -128,58 +140,37 @@
     <t>Punto de arranque</t>
   </si>
   <si>
-    <t>3432620076180</t>
-  </si>
-  <si>
-    <t>JERINGA 5 ML, 21 G, 1 - 1 1/2</t>
-  </si>
-  <si>
-    <t>GUANTES DE LATEX, TALLA PEQUEÑO</t>
-  </si>
-  <si>
-    <t>3214001002</t>
-  </si>
-  <si>
-    <t>DICLOFENACO LIQUIDO PARENTERAL 25 MG/ML CJ X AMP(S) X 3 ML</t>
-  </si>
-  <si>
-    <t>2025-04-16</t>
-  </si>
-  <si>
-    <t>CODIGO-INEXISTENTE-999</t>
-  </si>
-  <si>
-    <t>CODIGO NO ENCONTRADO EN CATALOGO</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
+    <t>EM21-65</t>
   </si>
   <si>
     <t>TOTAL VALOR SOLICITADO</t>
   </si>
   <si>
-    <t>Cero Dólares 08/100</t>
+    <t>Veinte Dólares 57/100</t>
   </si>
   <si>
     <t>NOMBRE:</t>
   </si>
   <si>
-    <t>VERONICA ELIZABETH CANTOS GAVILANES</t>
+    <t>Ana Torres</t>
   </si>
   <si>
     <t>DOCUMENTO DE IDENTIDAD:</t>
   </si>
   <si>
+    <t>1712345678</t>
+  </si>
+  <si>
     <t xml:space="preserve">CARGO: </t>
   </si>
   <si>
     <t>ANALISTA - FACTURACIÓN</t>
   </si>
   <si>
-    <t>FIRMA Y SELLO</t>
-  </si>
-  <si>
-    <t>JAIME MIGUEL CASTILLO CHANGUAN</t>
+    <t>Carlos Vega</t>
+  </si>
+  <si>
+    <t>1798765432</t>
   </si>
   <si>
     <t>DIRECTOR ADMINISTRATIVO</t>
@@ -664,7 +655,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1207,8 +1198,7 @@
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
       <c r="G6" s="20">
-        <f>[1]MATRIZ!K4</f>
-        <v>45762</v>
+        <v>46235</v>
       </c>
       <c r="H6" s="21"/>
       <c r="I6" s="22"/>
@@ -1219,15 +1209,13 @@
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="23">
-        <f>+I54</f>
-        <v>0.08</v>
+        <v>20.57</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="24" t="str">
-        <f>VLOOKUP(B5,[1]MATRIZ!A:G,5,0)</f>
-        <v>S720</v>
+      <c r="E7" s="24" t="s">
+        <v>9</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="18"/>
@@ -1236,10 +1224,12 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="19"/>
-      <c r="C8" s="18"/>
+      <c r="C8" s="18" t="s">
+        <v>11</v>
+      </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
@@ -1249,12 +1239,11 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B9" s="26"/>
-      <c r="C9" s="27">
-        <f>VLOOKUP(B5,[1]MATRIZ!A:G,4,0)</f>
-        <v>1701141028</v>
+      <c r="C9" s="27" t="s">
+        <v>13</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="18"/>
@@ -1265,12 +1254,11 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B10" s="17"/>
-      <c r="C10" s="28" t="str">
-        <f>VLOOKUP(B5,[1]MATRIZ!A:G,2,0)</f>
-        <v>CHILIG CHANGOLUISA MARIA ROSA</v>
+      <c r="C10" s="28" t="s">
+        <v>15</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
@@ -1281,21 +1269,19 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C11" s="31">
-        <f>VLOOKUP(B5,[1]MATRIZ!A:G,6,0)</f>
-        <v>45762</v>
+        <v>45945</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E11" s="31">
-        <f>C11</f>
-        <v>45762</v>
+        <v>45945</v>
       </c>
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
@@ -1304,86 +1290,86 @@
     </row>
     <row r="12" ht="38.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H12" s="34" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I12" s="35" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="36">
+        <v>45945</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="36">
         <v>1</v>
       </c>
-      <c r="B13" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="36" t="s">
-        <v>26</v>
-      </c>
       <c r="E13" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="36">
-        <v>1.74</v>
-      </c>
-      <c r="G13" s="36">
-        <v>1.74</v>
+        <v>0</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>29</v>
       </c>
       <c r="H13" s="36">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I13" s="36">
-        <v>1.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="37.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
-        <v>2</v>
+        <v>45945</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>28</v>
+        <v>11</v>
+      </c>
+      <c r="D14" s="36">
+        <v>1</v>
       </c>
       <c r="E14" s="36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" s="36">
         <v>0</v>
       </c>
-      <c r="G14" s="36">
-        <v>0</v>
+      <c r="G14" s="36" t="s">
+        <v>31</v>
       </c>
       <c r="H14" s="36">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I14" s="36">
         <v>0</v>
@@ -1391,28 +1377,28 @@
     </row>
     <row r="15" ht="39" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
-        <v>3</v>
+        <v>45945</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>28</v>
+        <v>11</v>
+      </c>
+      <c r="D15" s="36">
+        <v>4</v>
       </c>
       <c r="E15" s="36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" s="36">
         <v>0</v>
       </c>
-      <c r="G15" s="36">
-        <v>0</v>
+      <c r="G15" s="36" t="s">
+        <v>31</v>
       </c>
       <c r="H15" s="36">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I15" s="36">
         <v>0</v>
@@ -1420,656 +1406,292 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
-        <v>4</v>
+        <v>45945</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="36" t="s">
-        <v>28</v>
+        <v>11</v>
+      </c>
+      <c r="D16" s="36">
+        <v>1</v>
       </c>
       <c r="E16" s="36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F16" s="36">
-        <v>1.34</v>
-      </c>
-      <c r="G16" s="36">
-        <v>4.02</v>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>34</v>
       </c>
       <c r="H16" s="36">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I16" s="36">
-        <v>4.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
-        <v>5</v>
+        <v>45945</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="36" t="s">
-        <v>30</v>
+        <v>36</v>
+      </c>
+      <c r="D17" s="36">
+        <v>1</v>
       </c>
       <c r="E17" s="36">
-        <v>4</v>
+        <v>20.57</v>
       </c>
       <c r="F17" s="36">
-        <v>0.07</v>
-      </c>
-      <c r="G17" s="36">
-        <v>0.28</v>
+        <v>20.57</v>
+      </c>
+      <c r="G17" s="36" t="s">
+        <v>37</v>
       </c>
       <c r="H17" s="36">
         <v>100</v>
       </c>
       <c r="I17" s="36">
-        <v>0.28</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="36">
-        <v>6</v>
-      </c>
-      <c r="B18" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="36">
-        <v>1</v>
-      </c>
-      <c r="F18" s="36">
-        <v>0</v>
-      </c>
-      <c r="G18" s="36">
-        <v>0</v>
-      </c>
-      <c r="H18" s="36">
-        <v>1</v>
-      </c>
-      <c r="I18" s="36">
-        <v>0</v>
-      </c>
+      <c r="A18" s="36"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="36">
-        <v>7</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="36">
-        <v>1</v>
-      </c>
-      <c r="F19" s="36">
-        <v>0</v>
-      </c>
-      <c r="G19" s="36">
-        <v>0</v>
-      </c>
-      <c r="H19" s="36">
-        <v>1</v>
-      </c>
-      <c r="I19" s="36">
-        <v>0</v>
-      </c>
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="36">
-        <v>8</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="36">
-        <v>4</v>
-      </c>
-      <c r="F20" s="36">
-        <v>0</v>
-      </c>
-      <c r="G20" s="36">
-        <v>0</v>
-      </c>
-      <c r="H20" s="36">
-        <v>1</v>
-      </c>
-      <c r="I20" s="36">
-        <v>0</v>
-      </c>
+      <c r="A20" s="36"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="36">
-        <v>9</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="36">
-        <v>1</v>
-      </c>
-      <c r="F21" s="36">
-        <v>0</v>
-      </c>
-      <c r="G21" s="36">
-        <v>0</v>
-      </c>
-      <c r="H21" s="36">
-        <v>1</v>
-      </c>
-      <c r="I21" s="36">
-        <v>0</v>
-      </c>
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="36">
-        <v>10</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="36">
-        <v>1</v>
-      </c>
-      <c r="F22" s="36">
-        <v>0</v>
-      </c>
-      <c r="G22" s="36">
-        <v>0</v>
-      </c>
-      <c r="H22" s="36">
-        <v>1</v>
-      </c>
-      <c r="I22" s="36">
-        <v>0</v>
-      </c>
+      <c r="A22" s="36"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="36">
-        <v>11</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="36">
-        <v>1</v>
-      </c>
-      <c r="F23" s="36">
-        <v>0</v>
-      </c>
-      <c r="G23" s="36">
-        <v>0</v>
-      </c>
-      <c r="H23" s="36">
-        <v>1</v>
-      </c>
-      <c r="I23" s="36">
-        <v>0</v>
-      </c>
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="36">
-        <v>12</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="36">
-        <v>1</v>
-      </c>
-      <c r="F24" s="36">
-        <v>0</v>
-      </c>
-      <c r="G24" s="36">
-        <v>0</v>
-      </c>
-      <c r="H24" s="36">
-        <v>1</v>
-      </c>
-      <c r="I24" s="36">
-        <v>0</v>
-      </c>
+      <c r="A24" s="36"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="36">
-        <v>13</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="36">
-        <v>4</v>
-      </c>
-      <c r="F25" s="36">
-        <v>0</v>
-      </c>
-      <c r="G25" s="36">
-        <v>0</v>
-      </c>
-      <c r="H25" s="36">
-        <v>1</v>
-      </c>
-      <c r="I25" s="36">
-        <v>0</v>
-      </c>
+      <c r="A25" s="36"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="36">
-        <v>14</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="36">
-        <v>1</v>
-      </c>
-      <c r="F26" s="36">
-        <v>0</v>
-      </c>
-      <c r="G26" s="36">
-        <v>0</v>
-      </c>
-      <c r="H26" s="36">
-        <v>1</v>
-      </c>
-      <c r="I26" s="36">
-        <v>0</v>
-      </c>
+      <c r="A26" s="36"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="36">
-        <v>15</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="36">
-        <v>1</v>
-      </c>
-      <c r="F27" s="36">
-        <v>20.57</v>
-      </c>
-      <c r="G27" s="36">
-        <v>20.57</v>
-      </c>
-      <c r="H27" s="36">
-        <v>1</v>
-      </c>
-      <c r="I27" s="36">
-        <v>20.78</v>
-      </c>
+      <c r="A27" s="36"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="36">
-        <v>16</v>
-      </c>
-      <c r="B28" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="36">
-        <v>1</v>
-      </c>
-      <c r="F28" s="36">
-        <v>0.05</v>
-      </c>
-      <c r="G28" s="36">
-        <v>0.05</v>
-      </c>
-      <c r="H28" s="36">
-        <v>1</v>
-      </c>
-      <c r="I28" s="36">
-        <v>0.05</v>
-      </c>
+      <c r="A28" s="36"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="36">
-        <v>17</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="E29" s="36">
-        <v>1</v>
-      </c>
-      <c r="F29" s="36">
-        <v>0.08</v>
-      </c>
-      <c r="G29" s="36">
-        <v>0.08</v>
-      </c>
-      <c r="H29" s="36">
-        <v>1</v>
-      </c>
-      <c r="I29" s="36">
-        <v>0.08</v>
-      </c>
+      <c r="A29" s="36"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="36">
-        <v>18</v>
-      </c>
-      <c r="B30" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="36">
-        <v>4</v>
-      </c>
-      <c r="F30" s="36">
-        <v>0.07</v>
-      </c>
-      <c r="G30" s="36">
-        <v>0.28</v>
-      </c>
-      <c r="H30" s="36">
-        <v>1</v>
-      </c>
-      <c r="I30" s="36">
-        <v>0.28</v>
-      </c>
+      <c r="A30" s="36"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="36">
-        <v>19</v>
-      </c>
-      <c r="B31" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="36">
-        <v>1</v>
-      </c>
-      <c r="F31" s="36">
-        <v>1.74</v>
-      </c>
-      <c r="G31" s="36">
-        <v>1.74</v>
-      </c>
-      <c r="H31" s="36">
-        <v>1</v>
-      </c>
-      <c r="I31" s="36">
-        <v>1.74</v>
-      </c>
+      <c r="A31" s="36"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="36">
-        <v>20</v>
-      </c>
-      <c r="B32" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="36">
-        <v>1</v>
-      </c>
-      <c r="F32" s="36">
-        <v>0</v>
-      </c>
-      <c r="G32" s="36">
-        <v>0</v>
-      </c>
-      <c r="H32" s="36">
-        <v>1</v>
-      </c>
-      <c r="I32" s="36">
-        <v>0.13</v>
-      </c>
+      <c r="A32" s="36"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="36">
-        <v>21</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="36">
-        <v>1</v>
-      </c>
-      <c r="F33" s="36">
-        <v>20.57</v>
-      </c>
-      <c r="G33" s="36">
-        <v>20.57</v>
-      </c>
-      <c r="H33" s="36">
-        <v>1</v>
-      </c>
-      <c r="I33" s="36">
-        <v>20.78</v>
-      </c>
+      <c r="A33" s="36"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="36">
-        <v>22</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" s="36">
-        <v>1</v>
-      </c>
-      <c r="F34" s="36">
-        <v>0.05</v>
-      </c>
-      <c r="G34" s="36">
-        <v>0.05</v>
-      </c>
-      <c r="H34" s="36">
-        <v>1</v>
-      </c>
-      <c r="I34" s="36">
-        <v>0.05</v>
-      </c>
+      <c r="A34" s="36"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="36">
-        <v>23</v>
-      </c>
-      <c r="B35" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="36">
-        <v>1</v>
-      </c>
-      <c r="F35" s="36">
-        <v>0.08</v>
-      </c>
-      <c r="G35" s="36">
-        <v>0.08</v>
-      </c>
-      <c r="H35" s="36">
-        <v>1</v>
-      </c>
-      <c r="I35" s="36">
-        <v>0.08</v>
-      </c>
+      <c r="A35" s="36"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="36">
-        <v>24</v>
-      </c>
-      <c r="B36" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="36">
-        <v>4</v>
-      </c>
-      <c r="F36" s="36">
-        <v>0.07</v>
-      </c>
-      <c r="G36" s="36">
-        <v>0.28</v>
-      </c>
-      <c r="H36" s="36">
-        <v>1</v>
-      </c>
-      <c r="I36" s="36">
-        <v>0.28</v>
-      </c>
+      <c r="A36" s="36"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="36">
-        <v>25</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="36">
-        <v>1</v>
-      </c>
-      <c r="F37" s="36">
-        <v>0.15</v>
-      </c>
-      <c r="G37" s="36">
-        <v>0.15</v>
-      </c>
-      <c r="H37" s="36">
-        <v>0</v>
-      </c>
-      <c r="I37" s="36">
-        <v>1</v>
-      </c>
+      <c r="A37" s="36"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="36"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="36"/>
       <c r="B38" s="36"/>
       <c r="C38" s="36"/>
-      <c r="D38" s="36" t="s">
-        <v>41</v>
-      </c>
+      <c r="D38" s="36"/>
       <c r="E38" s="36"/>
       <c r="F38" s="36"/>
       <c r="G38" s="36"/>
       <c r="H38" s="36"/>
-      <c r="I38" s="36">
-        <v>51.33</v>
-      </c>
+      <c r="I38" s="36"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="36"/>
@@ -2226,50 +1848,23 @@
       <c r="I52" s="36"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="36">
-        <f>IF(#REF!=0,"",#REF!)</f>
-        <v>NaN</v>
-      </c>
-      <c r="B53" s="37" t="e">
-        <f>IF(#REF!=0,"",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C53" s="33" t="e">
-        <f>IF(#REF!=0,"",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D53" s="33" t="e">
-        <f>IF(#REF!=0,"",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E53" s="33" t="e">
-        <f>IF(#REF!=0,"",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F53" s="34" t="e">
-        <f t="shared" ref="F53" si="0">IF(OR(NOT(ISNUMBER(D53)),D53=0),"",D53*E53)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G53" s="34" t="e">
-        <f>IF(#REF!=0," ",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H53" s="38" t="e">
-        <f>IF(#REF!=0,"",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I53" s="35" t="e">
-        <f t="shared" ref="I53" si="1">IF(F53=0," ",F53)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="A53" s="36"/>
+      <c r="B53" s="37"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="35"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="39" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B54" s="39"/>
       <c r="C54" s="40" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D54" s="41"/>
       <c r="E54" s="41"/>
@@ -2277,412 +1872,186 @@
       <c r="G54" s="41"/>
       <c r="H54" s="42"/>
       <c r="I54" s="43">
-        <v>0.08</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="55" ht="90.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="44">
-        <v>1</v>
-      </c>
-      <c r="B55" s="45">
-        <v>1</v>
-      </c>
-      <c r="C55" s="45">
-        <v>1</v>
-      </c>
-      <c r="D55" s="45">
-        <v>1</v>
-      </c>
-      <c r="E55" s="45">
-        <v>1</v>
-      </c>
-      <c r="F55" s="45">
-        <v>1</v>
-      </c>
-      <c r="G55" s="45">
-        <v>1</v>
-      </c>
-      <c r="H55" s="45">
-        <v>1</v>
-      </c>
-      <c r="I55" s="46">
-        <v>1</v>
-      </c>
+      <c r="A55" s="44"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="45"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="45"/>
+      <c r="G55" s="45"/>
+      <c r="H55" s="45"/>
+      <c r="I55" s="46"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="47">
-        <v>1</v>
-      </c>
-      <c r="B56" s="48">
-        <v>1</v>
-      </c>
-      <c r="C56" s="48">
-        <v>1</v>
-      </c>
-      <c r="D56" s="48">
-        <v>1</v>
-      </c>
-      <c r="E56" s="48">
-        <v>1</v>
-      </c>
-      <c r="F56" s="48">
-        <v>1</v>
-      </c>
-      <c r="G56" s="48">
-        <v>1</v>
-      </c>
-      <c r="H56" s="48">
-        <v>1</v>
-      </c>
-      <c r="I56" s="49">
-        <v>1</v>
-      </c>
+      <c r="A56" s="47"/>
+      <c r="B56" s="48"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
+      <c r="H56" s="48"/>
+      <c r="I56" s="49"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="47">
-        <v>1</v>
-      </c>
-      <c r="B57" s="48">
-        <v>1</v>
-      </c>
-      <c r="C57" s="48">
-        <v>1</v>
-      </c>
-      <c r="D57" s="48">
-        <v>1</v>
-      </c>
-      <c r="E57" s="48">
-        <v>1</v>
-      </c>
-      <c r="F57" s="48">
-        <v>1</v>
-      </c>
-      <c r="G57" s="48">
-        <v>1</v>
-      </c>
-      <c r="H57" s="48">
-        <v>1</v>
-      </c>
-      <c r="I57" s="49">
-        <v>1</v>
-      </c>
+      <c r="A57" s="47"/>
+      <c r="B57" s="48"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="48"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="49"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="47">
-        <v>1</v>
-      </c>
-      <c r="B58" s="48">
-        <v>1</v>
-      </c>
-      <c r="C58" s="48">
-        <v>1</v>
-      </c>
-      <c r="D58" s="48">
-        <v>1</v>
-      </c>
-      <c r="E58" s="48">
-        <v>1</v>
-      </c>
-      <c r="F58" s="48">
-        <v>1</v>
-      </c>
-      <c r="G58" s="48">
-        <v>1</v>
-      </c>
-      <c r="H58" s="48">
-        <v>1</v>
-      </c>
-      <c r="I58" s="49">
-        <v>1</v>
-      </c>
+      <c r="A58" s="47"/>
+      <c r="B58" s="48"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="48"/>
+      <c r="I58" s="49"/>
     </row>
     <row r="59" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="47">
-        <v>1</v>
-      </c>
-      <c r="B59" s="48">
-        <v>1</v>
-      </c>
-      <c r="C59" s="48">
-        <v>1</v>
-      </c>
-      <c r="D59" s="48">
-        <v>1</v>
-      </c>
-      <c r="E59" s="48">
-        <v>1</v>
-      </c>
-      <c r="F59" s="48">
-        <v>1</v>
-      </c>
-      <c r="G59" s="48">
-        <v>1</v>
-      </c>
-      <c r="H59" s="48">
-        <v>1</v>
-      </c>
-      <c r="I59" s="49">
-        <v>1</v>
-      </c>
+      <c r="A59" s="47"/>
+      <c r="B59" s="48"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="48"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="49"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="47">
-        <v>1</v>
-      </c>
+      <c r="A60" s="47"/>
       <c r="B60" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C60" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="52"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="53"/>
+      <c r="H60" s="53"/>
+      <c r="I60" s="54"/>
+    </row>
+    <row r="61" ht="25.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="47"/>
+      <c r="B61" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C61" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61" s="53"/>
+      <c r="E61" s="53"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53"/>
+      <c r="H61" s="53"/>
+      <c r="I61" s="54"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="47"/>
+      <c r="B62" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C60" s="51" t="s">
+      <c r="C62" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="D60" s="52"/>
-      <c r="E60" s="53">
-        <v>1</v>
-      </c>
-      <c r="F60" s="53">
-        <v>1</v>
-      </c>
-      <c r="G60" s="53">
-        <v>1</v>
-      </c>
-      <c r="H60" s="53">
-        <v>1</v>
-      </c>
-      <c r="I60" s="54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" ht="25.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="47">
-        <v>1</v>
-      </c>
-      <c r="B61" s="55" t="s">
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="59"/>
+      <c r="H62" s="60"/>
+      <c r="I62" s="61"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="47"/>
+      <c r="B63" s="53"/>
+      <c r="C63" s="53"/>
+      <c r="D63" s="53"/>
+      <c r="E63" s="53"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53"/>
+      <c r="H63" s="53"/>
+      <c r="I63" s="61"/>
+    </row>
+    <row r="64" ht="72.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="47"/>
+      <c r="B64" s="53"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="53"/>
+      <c r="H64" s="53"/>
+      <c r="I64" s="54"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="47"/>
+      <c r="B65" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C65" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="C61" s="56">
-        <v>603665530</v>
-      </c>
-      <c r="D61" s="53">
-        <v>1</v>
-      </c>
-      <c r="E61" s="53">
-        <v>1</v>
-      </c>
-      <c r="F61" s="53">
-        <v>1</v>
-      </c>
-      <c r="G61" s="53">
-        <v>1</v>
-      </c>
-      <c r="H61" s="53">
-        <v>1</v>
-      </c>
-      <c r="I61" s="54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="47">
-        <v>1</v>
-      </c>
-      <c r="B62" s="57" t="s">
+      <c r="D65" s="53"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53"/>
+      <c r="H65" s="53"/>
+      <c r="I65" s="54"/>
+    </row>
+    <row r="66" ht="25.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="47"/>
+      <c r="B66" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C66" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="C62" s="58" t="s">
+      <c r="D66" s="53"/>
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="53"/>
+      <c r="I66" s="54"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="47"/>
+      <c r="B67" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="D62" s="53">
-        <v>1</v>
-      </c>
-      <c r="E62" s="53">
-        <v>1</v>
-      </c>
-      <c r="F62" s="53">
-        <v>1</v>
-      </c>
-      <c r="G62" s="59" t="s">
-        <v>49</v>
-      </c>
-      <c r="H62" s="60">
-        <v>1</v>
-      </c>
-      <c r="I62" s="61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="47">
-        <v>1</v>
-      </c>
-      <c r="B63" s="53">
-        <v>1</v>
-      </c>
-      <c r="C63" s="53">
-        <v>1</v>
-      </c>
-      <c r="D63" s="53">
-        <v>1</v>
-      </c>
-      <c r="E63" s="53">
-        <v>1</v>
-      </c>
-      <c r="F63" s="53">
-        <v>1</v>
-      </c>
-      <c r="G63" s="53">
-        <v>1</v>
-      </c>
-      <c r="H63" s="53">
-        <v>1</v>
-      </c>
-      <c r="I63" s="61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" ht="72.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="47">
-        <v>1</v>
-      </c>
-      <c r="B64" s="53">
-        <v>1</v>
-      </c>
-      <c r="C64" s="53">
-        <v>1</v>
-      </c>
-      <c r="D64" s="53">
-        <v>1</v>
-      </c>
-      <c r="E64" s="53">
-        <v>1</v>
-      </c>
-      <c r="F64" s="53">
-        <v>1</v>
-      </c>
-      <c r="G64" s="53">
-        <v>1</v>
-      </c>
-      <c r="H64" s="53">
-        <v>1</v>
-      </c>
-      <c r="I64" s="54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="47">
-        <v>1</v>
-      </c>
-      <c r="B65" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="C65" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="D65" s="53">
-        <v>1</v>
-      </c>
-      <c r="E65" s="53">
-        <v>1</v>
-      </c>
-      <c r="F65" s="53">
-        <v>1</v>
-      </c>
-      <c r="G65" s="53">
-        <v>1</v>
-      </c>
-      <c r="H65" s="53">
-        <v>1</v>
-      </c>
-      <c r="I65" s="54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" ht="25.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="47">
-        <v>1</v>
-      </c>
-      <c r="B66" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66" s="56">
-        <v>400821997</v>
-      </c>
-      <c r="D66" s="53">
-        <v>1</v>
-      </c>
-      <c r="E66" s="53">
-        <v>1</v>
-      </c>
-      <c r="F66" s="53">
-        <v>1</v>
-      </c>
-      <c r="G66" s="53">
-        <v>1</v>
-      </c>
-      <c r="H66" s="53">
-        <v>1</v>
-      </c>
-      <c r="I66" s="54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="47">
-        <v>1</v>
-      </c>
-      <c r="B67" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="C67" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="D67" s="53">
-        <v>1</v>
-      </c>
-      <c r="E67" s="53">
-        <v>1</v>
-      </c>
-      <c r="F67" s="53">
-        <v>1</v>
-      </c>
-      <c r="G67" s="59" t="s">
-        <v>49</v>
-      </c>
-      <c r="H67" s="60">
-        <v>1</v>
-      </c>
-      <c r="I67" s="54">
-        <v>1</v>
-      </c>
+      <c r="D67" s="53"/>
+      <c r="E67" s="53"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="59"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="54"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="62">
-        <v>1</v>
-      </c>
-      <c r="B68" s="60">
-        <v>1</v>
-      </c>
-      <c r="C68" s="60">
-        <v>1</v>
-      </c>
-      <c r="D68" s="60">
-        <v>1</v>
-      </c>
-      <c r="E68" s="60">
-        <v>1</v>
-      </c>
-      <c r="F68" s="60">
-        <v>1</v>
-      </c>
-      <c r="G68" s="60">
-        <v>1</v>
-      </c>
-      <c r="H68" s="60">
-        <v>1</v>
-      </c>
-      <c r="I68" s="63">
-        <v>1</v>
-      </c>
+      <c r="A68" s="62"/>
+      <c r="B68" s="60"/>
+      <c r="C68" s="60"/>
+      <c r="D68" s="60"/>
+      <c r="E68" s="60"/>
+      <c r="F68" s="60"/>
+      <c r="G68" s="60"/>
+      <c r="H68" s="60"/>
+      <c r="I68" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="6">
